--- a/downloads/10.5281_zenodo.19682162/cb_hbm4eu_alignedstudies_teenagers.xlsx
+++ b/downloads/10.5281_zenodo.19682162/cb_hbm4eu_alignedstudies_teenagers.xlsx
@@ -4304,22 +4304,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="61.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="208.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="127.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="70.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="82.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="192.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -4988,22 +4972,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="33.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="4.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="87.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -5116,22 +5084,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="133.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="29.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="58.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="56.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -5688,22 +5640,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="25.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="250.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="47.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="250.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="115.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="84.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -11868,22 +11804,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="126.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="192.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="250.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -17692,22 +17612,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="211.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="8.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="62.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="250.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="70.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -18516,11 +18420,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="52.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="172.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -18722,11 +18621,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="8.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="132.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
